--- a/naver-place-crawler/results_health/북구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/북구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+          <t>웰니스 피트니스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>body7677@naver.com</t>
+          <t>pingdi@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1388-7681</t>
+          <t>0507-1384-1311</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+          <t>대구광역시 북구 칠곡중앙대로 475 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyengineers_kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1433</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1912</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>3345</v>
+        <v>5</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1961345457</t>
+          <t>1044132328</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961345457</t>
+          <t>https://m.place.naver.com/place/1044132328</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>지젤 칠곡점 헬스 PT GX 요가</t>
+          <t>욱스짐 도남점 헬스PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>giselle331704@naver.com</t>
+          <t>thenamja89@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1321-6496</t>
+          <t>0507-1329-3354</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동암로 90 3층</t>
+          <t>대구광역시 북구 도남중앙로8길 1 시그니쳐타워 7층 욱스짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+          <t>https://www.instagram.com/wook_s_gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1235</v>
+        <v>752</v>
       </c>
       <c r="Q3" t="n">
-        <v>538</v>
+        <v>218</v>
       </c>
       <c r="R3" t="n">
-        <v>1773</v>
+        <v>970</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1616049160</t>
+          <t>1340689579</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616049160</t>
+          <t>https://m.place.naver.com/place/1340689579</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스보이짐 롯데대구역점</t>
+          <t>원나인피트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>healthboygym86@naver.com</t>
+          <t>fhdnzlr892@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1439-0444</t>
+          <t>1800-6672</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태평로 161 9층</t>
+          <t>대구광역시 북구 호암로 6 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy86</t>
+          <t>https://blog.naver.com/fhdnzlr892</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>436</v>
+        <v>194</v>
       </c>
       <c r="Q4" t="n">
-        <v>146</v>
+        <v>606</v>
       </c>
       <c r="R4" t="n">
-        <v>582</v>
+        <v>800</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,56 +824,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1966515992</t>
+          <t>1696346241</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966515992</t>
+          <t>https://m.place.naver.com/place/1696346241</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>레드짐 복현오거리점 헬스 &amp; PT</t>
+          <t>FM피트니스 동천점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>redgym8555@naver.com</t>
+          <t>teran0120@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>053-1877-3632</t>
+          <t>0507-1472-9699</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 북구 검단로 9 3층, 4층</t>
+          <t>대구광역시 북구 대천로 90 4층,5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/redgym_b5</t>
+          <t>https://www.instagram.com/fm_fitness96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>809</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="n">
-        <v>660</v>
+        <v>40</v>
       </c>
       <c r="R5" t="n">
-        <v>1469</v>
+        <v>63</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1813814971</t>
+          <t>1811078908</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813814971</t>
+          <t>https://m.place.naver.com/place/1811078908</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>레드짐 침산점 헬스&amp;스파</t>
+          <t>포레스트짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>redgym-chim@naver.com</t>
+          <t>forestgym-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1329-5605</t>
+          <t>0507-1482-0831</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 138 6층</t>
+          <t>대구광역시 북구 칠성남로 43 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/redgym_chimsan</t>
+          <t>https://www.instagram.com/forestgym_/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>384</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>221</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>605</v>
+        <v>40</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,47 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1070126824</t>
+          <t>1186829756</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070126824</t>
+          <t>https://m.place.naver.com/place/1186829756</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>조지아 헬스 PT 스피닝 GX 칠곡점</t>
+          <t>레드워크아웃 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gogia4879@naver.com</t>
+          <t>siytg1234@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1383-4879</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 133 701호,702호,703호</t>
+          <t>대구광역시 북구 복현로 127 4층,5층 레드워크아웃 (성화여고건너, 봄봄 건물)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/georgia.one1</t>
+          <t>https://blog.naver.com/siytg1234</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="Q7" t="n">
-        <v>444</v>
+        <v>241</v>
       </c>
       <c r="R7" t="n">
-        <v>715</v>
+        <v>496</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1102,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1013813873</t>
+          <t>1179762159</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013813873</t>
+          <t>https://m.place.naver.com/place/1179762159</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>욱스짐 도남점 헬스PT</t>
+          <t>어바웃더핏 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>thenamja89@naver.com</t>
+          <t>mildodrax2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1329-3354</t>
+          <t>0507-1314-2445</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로8길 1 시그니쳐타워 7층 욱스짐</t>
+          <t>대구광역시 북구 학정로 149 태전동 1195 번지 4층, 어바웃더핏</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wook_s_gym</t>
+          <t>https://www.instagram.com/aboutthefit_gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>737</v>
+        <v>767</v>
       </c>
       <c r="Q8" t="n">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="R8" t="n">
-        <v>953</v>
+        <v>904</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1196,47 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1340689579</t>
+          <t>1258524487</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340689579</t>
+          <t>https://m.place.naver.com/place/1258524487</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>더레드짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>thered_gym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1398-9797</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구광역시 북구 복현로 105 태왕아너스상가 4층, 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>https://www.instagram.com/theredgym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>697</v>
+        <v>472</v>
       </c>
       <c r="Q9" t="n">
-        <v>771</v>
+        <v>159</v>
       </c>
       <c r="R9" t="n">
-        <v>1468</v>
+        <v>631</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,61 +1286,61 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1243559985</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1243559985</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스톤짐 복현점</t>
+          <t>그린짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>stonegym_3@naver.com</t>
+          <t>pk0236@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1333-5469</t>
+          <t>0507-1390-5563</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+          <t>대구광역시 북구 학정로 439 502호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pQdrxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1364,22 +1356,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>703</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>173</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>876</v>
+        <v>28</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1380,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1113466448</t>
+          <t>1007068851</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113466448</t>
+          <t>https://m.place.naver.com/place/1007068851</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피트온24 복현점</t>
+          <t>팀에스핏</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mave000@naver.com</t>
+          <t>moa0121moa@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1322-3225</t>
+          <t>0507-1414-7988</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
+          <t>대구광역시 북구 동북로 280 3,4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mave000</t>
+          <t>https://www.instagram.com/hee_moa0121</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1439,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2016</v>
+        <v>119</v>
       </c>
       <c r="Q11" t="n">
-        <v>888</v>
+        <v>83</v>
       </c>
       <c r="R11" t="n">
-        <v>2904</v>
+        <v>202</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,51 +1474,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1855565865</t>
+          <t>38258053</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855565865</t>
+          <t>https://m.place.naver.com/place/38258053</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피트온24 칠곡점</t>
+          <t>팀42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fitness240@naver.com</t>
+          <t>sun0799dh@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>053-313-8817</t>
+          <t>0507-1306-2047</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
+          <t>대구광역시 북구 원대로 76 지하1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness240</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1536,12 +1528,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1552,22 +1544,22 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2303</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>877</v>
+        <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>3180</v>
+        <v>11</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,51 +1568,51 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1175448883</t>
+          <t>1878169203</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1175448883</t>
+          <t>https://m.place.naver.com/place/1878169203</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>원나인피트니스</t>
+          <t>버거짐</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fhdnzlr892@naver.com</t>
+          <t>burgergym@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1800-6672</t>
+          <t>0507-1400-9556</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호암로 6 5층</t>
+          <t>대구광역시 북구 팔달로 209 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fhdnzlr892</t>
+          <t>https://www.instagram.com/burger_gym_</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1635,7 +1627,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1655,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="Q13" t="n">
-        <v>571</v>
+        <v>362</v>
       </c>
       <c r="R13" t="n">
-        <v>764</v>
+        <v>517</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,51 +1662,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1696346241</t>
+          <t>1590239180</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696346241</t>
+          <t>https://m.place.naver.com/place/1590239180</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>이지피트니스</t>
+          <t>태양헬스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>easyfitness01@naver.com</t>
+          <t>dnrlek78@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1350-1029</t>
+          <t>053-324-1236</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
+          <t>대구광역시 북구 칠곡중앙대로 423 태양헬스 9층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/easyfitness01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1724,12 +1716,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1745,17 +1737,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>605</v>
+        <v>48</v>
       </c>
       <c r="Q14" t="n">
-        <v>283</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>888</v>
+        <v>53</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,51 +1756,47 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1129757069</t>
+          <t>37992328</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129757069</t>
+          <t>https://m.place.naver.com/place/37992328</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>마인드휘트니스 도남점</t>
+          <t>리브</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mindfitness21@naver.com</t>
+          <t>ekgus1002@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1490-0792</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로7길 20-4 601호</t>
+          <t>대구광역시 북구 침산남로 180-6 지하1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness21</t>
+          <t>https://www.instagram.com/lib_official_/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1823,7 +1811,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1843,13 +1831,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>821</v>
+        <v>19</v>
       </c>
       <c r="Q15" t="n">
-        <v>249</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1070</v>
+        <v>23</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,51 +1846,51 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1552558325</t>
+          <t>2045901558</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1552558325</t>
+          <t>https://m.place.naver.com/place/2045901558</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>탑클래스짐 서변점</t>
+          <t>더퍼스트 피트니스 칠곡점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>topclass_gym@naver.com</t>
+          <t>tffpceo10@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1393-3466</t>
+          <t>0507-1304-3714</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로 227 5층</t>
+          <t>대구광역시 북구 동천로 125 5층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/topclass_gym</t>
+          <t>https://blog.naver.com/tffpceo10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1937,13 +1925,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="Q16" t="n">
-        <v>164</v>
+        <v>280</v>
       </c>
       <c r="R16" t="n">
-        <v>384</v>
+        <v>588</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,51 +1940,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1042649945</t>
+          <t>1040934279</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1042649945</t>
+          <t>https://m.place.naver.com/place/1040934279</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FM피트니스</t>
+          <t>바디채널 침산점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>teran0120@naver.com</t>
+          <t>bodycs@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1326-7507</t>
+          <t>0507-1342-4850</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로 80-1 태백빌딩 6층</t>
+          <t>대구광역시 북구 침산남로 154 10층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teran0120</t>
+          <t>https://www.instagram.com/bodychannel_chimsan</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2011,7 +1999,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2031,13 +2019,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="Q17" t="n">
-        <v>111</v>
+        <v>1529</v>
       </c>
       <c r="R17" t="n">
-        <v>163</v>
+        <v>1706</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,47 +2034,51 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1115611185</t>
+          <t>1023076989</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115611185</t>
+          <t>https://m.place.naver.com/place/1023076989</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>트라이핏 복현푸르지오점</t>
+          <t>지젤 노원점 헬스 PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>trifit4@naver.com</t>
+          <t>giselle331709@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1342-7936</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 325 3, 4층</t>
+          <t>대구광역시 북구 팔달로35길 20 5층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/trifit_bokhyeon</t>
+          <t>https://blog.naver.com/giselle331709</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2101,7 +2093,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2121,13 +2113,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>111</v>
+        <v>475</v>
       </c>
       <c r="Q18" t="n">
-        <v>153</v>
+        <v>493</v>
       </c>
       <c r="R18" t="n">
-        <v>264</v>
+        <v>968</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,51 +2128,51 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1875195371</t>
+          <t>1294730549</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875195371</t>
+          <t>https://m.place.naver.com/place/1294730549</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>버거짐</t>
+          <t>FM피트니스 태전점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>burgergym@naver.com</t>
+          <t>werxman@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1400-9556</t>
+          <t>0507-1336-9688</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로 209 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로 269 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/burger_gym_</t>
+          <t>https://www.instagram.com/fmfitness9696</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2215,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="Q19" t="n">
-        <v>359</v>
+        <v>129</v>
       </c>
       <c r="R19" t="n">
-        <v>513</v>
+        <v>187</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,51 +2222,51 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1590239180</t>
+          <t>1649195059</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1590239180</t>
+          <t>https://m.place.naver.com/place/1649195059</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>원나인피트니스 침산점</t>
+          <t>써니짐 침산점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>oneninegym_chimsan@naver.com</t>
+          <t>cheyeong_007@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1800-9533</t>
+          <t>053-341-1588</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 96 2층 201호</t>
+          <t>대구광역시 북구 침산남로 96 501호 502호 503호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oneninegym_chimsan</t>
+          <t>https://www.instagram.com/sunnygym_official</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2289,7 +2281,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2309,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>218</v>
+        <v>1392</v>
       </c>
       <c r="Q20" t="n">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="R20" t="n">
-        <v>353</v>
+        <v>1561</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,51 +2316,51 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1682965261</t>
+          <t>1534903715</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682965261</t>
+          <t>https://m.place.naver.com/place/1534903715</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>지젤피트니스클럽 노원점</t>
+          <t>탑클래스짐 서변점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>giselle331709@naver.com</t>
+          <t>topclass_gym@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1342-7936</t>
+          <t>0507-1393-3466</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로35길 20 5층</t>
+          <t>대구광역시 북구 호국로 227 5층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/giselle331709</t>
+          <t>https://blog.naver.com/topclass_gym</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2403,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>475</v>
+        <v>225</v>
       </c>
       <c r="Q21" t="n">
-        <v>486</v>
+        <v>165</v>
       </c>
       <c r="R21" t="n">
-        <v>961</v>
+        <v>390</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2410,5175 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1294730549</t>
+          <t>1042649945</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294730549</t>
+          <t>https://m.place.naver.com/place/1042649945</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>아이디짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ildomin@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1319-9446</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 내곡로 73 금강프라자 3층 아이디헬스IDGYM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/idgym24h?igsh=MTBnOHl0a2M3enBxdQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>135</v>
+      </c>
+      <c r="R22" t="n">
+        <v>209</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1254581921</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1254581921</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>바디웨이 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>striver_ocean@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1488-2098</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 구암로 148 4, 5층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/striver_ocean</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>76</v>
+      </c>
+      <c r="R23" t="n">
+        <v>149</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1534494580</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1534494580</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>엔드짐</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>himy491@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>053-311-6939</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 매천로18길 29 5층, 엔드짐</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/endgym_official</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>14</v>
+      </c>
+      <c r="R24" t="n">
+        <v>43</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1314145805</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1314145805</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>피터짐</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>fitter_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1381-8120</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 옥산로 95 5층, 피터짐</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitter__gym</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>195</v>
+      </c>
+      <c r="R25" t="n">
+        <v>439</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1819328004</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1819328004</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>마인드휘트니스 도남점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mindfitness21@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1490-0792</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 도남중앙로7길 20-4 601호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mindfitness21</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>823</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>251</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1074</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1552558325</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1552558325</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>스타트짐</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ajfitness6262@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1457-6260</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 대현로 84 (농협건물) 3층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ajfitness6262</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>34</v>
+      </c>
+      <c r="R27" t="n">
+        <v>182</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>32693542</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32693542</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>스카이짐</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>pyup2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1432-9697</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학남로 95 2층 스카이짐</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pyup2000</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>42</v>
+      </c>
+      <c r="R28" t="n">
+        <v>62</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>60630663</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/60630663</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>스카이휘트니스 사우나</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>uvtt0407@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>053-956-8500</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 156 5층헬스장</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>110</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1560224728</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1560224728</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>데일리짐</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>zhqlqudrl@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1341-8555</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 158 건영하이츠 상가 (CU편의점 2층)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xmwltb</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>294</v>
+      </c>
+      <c r="R30" t="n">
+        <v>491</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>20771266</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20771266</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>레드짐 복현오거리점 헬스 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>redgym8555@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>053-1877-3632</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 검단로 9 3층, 4층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://litt.ly/redgym_b5</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>815</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>662</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1477</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1813814971</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1813814971</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>칠성휘트니스</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ukino2339@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1489-2039</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠성남로 101 101동</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/7sung_f</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>24</v>
+      </c>
+      <c r="R32" t="n">
+        <v>27</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1198192231</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1198192231</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>피트온24 복현점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>mave000@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1322-3225</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mave000</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>2020</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>980</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1855565865</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1855565865</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>트라이핏 복현푸르지오점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>trifit4@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 325 3, 4층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/trifit_bokhyeon</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>156</v>
+      </c>
+      <c r="R34" t="n">
+        <v>271</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1875195371</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1875195371</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FM피트니스</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>teran0120@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1326-7507</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 팔거천동로 80-1 태백빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teran0120</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>111</v>
+      </c>
+      <c r="R35" t="n">
+        <v>163</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1115611185</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1115611185</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>오짐 헬스&amp;PT 동천점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>forever7582@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1421-9655</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동천로 125-4 4층 오짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://m.site.naver.com/1CMKz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>657</v>
+      </c>
+      <c r="R36" t="n">
+        <v>964</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1264751882</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1264751882</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>맥시멈짐</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>maximum_si@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1310-3561</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 대현로 102 삼주빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/leetaekwan_classic</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>65</v>
+      </c>
+      <c r="R37" t="n">
+        <v>89</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1928149032</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928149032</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>크로스핏타임 칠곡점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>timegym2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1355-3967</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 팔거천동로 224 지하1층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/shs4uWwf</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>37</v>
+      </c>
+      <c r="R38" t="n">
+        <v>106</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1151810571</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1151810571</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>제로짐 복현</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>zerogym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 291 4층 제로짐</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/zerogym__</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>31</v>
+      </c>
+      <c r="R39" t="n">
+        <v>67</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2083396096</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2083396096</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>조지아 헬스 PT 스피닝 GX 칠곡점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gogia4879@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1383-4879</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동천로 133 701호,702호,703호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/georgia.one1</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>446</v>
+      </c>
+      <c r="R40" t="n">
+        <v>719</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1013813873</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1013813873</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>심피트니스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>simfitness24@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1483-1279</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 공항로 69-9 69-11, 외 2필지</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/simfitness24</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>452</v>
+      </c>
+      <c r="R41" t="n">
+        <v>776</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1569924819</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1569924819</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>원나인피트니스 침산점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>oneninegym_chimsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1800-9533</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산남로 96 2층 201호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/oneninegym_chimsan</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>135</v>
+      </c>
+      <c r="R42" t="n">
+        <v>354</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1682965261</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1682965261</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>지젤 칠곡점 헬스 PT GX 요가</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>giselle331704@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1321-6496</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동암로 90 3층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1241</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>544</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1785</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1616049160</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1616049160</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>월드짐 피트니스 센터</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>worldgym_cs@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>053-356-3600</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 142</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/worldgym_cs</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>71</v>
+      </c>
+      <c r="R44" t="n">
+        <v>89</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1802720489</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1802720489</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>레드짐 침산점 헬스&amp;스파</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>redgym-chim@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1329-5605</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 138 6층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/redgym_chimsan</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>224</v>
+      </c>
+      <c r="R45" t="n">
+        <v>616</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1070126824</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070126824</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>패러다임짐 복현점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>paradigm1378@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1346-1460</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 223 3층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/paradigm1378/223060126537</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>376</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>380</v>
+      </c>
+      <c r="R46" t="n">
+        <v>756</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1397098871</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397098871</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>나홀로짐</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bs4376@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>053-234-5678</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동변로16길 8-8</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://instagram.com/use_gym_alone?utm_medium=copy_link</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>9</v>
+      </c>
+      <c r="R47" t="n">
+        <v>63</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1237091070</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1237091070</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>빅토리짐 PT&amp;헬스 동천점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sjsjfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1370-1301</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동천로23길 36 2층 201호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sjsjfit</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>190</v>
+      </c>
+      <c r="R48" t="n">
+        <v>292</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1903714032</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1903714032</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>피트온24 칠곡점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>fitness240@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>053-313-8817</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitness240</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>2309</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>969</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3278</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1175448883</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1175448883</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>브이피트니스</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>vfitness3650@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1461-3654</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 매전로 80 , 3층 301호(태전동)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vfitness3650</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>24</v>
+      </c>
+      <c r="R50" t="n">
+        <v>63</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1866227499</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1866227499</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>헬스보이짐 롯데대구역점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>healthboygym86@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1439-0444</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 태평로 161 9층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/healthboy86</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>148</v>
+      </c>
+      <c r="R51" t="n">
+        <v>589</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1966515992</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1966515992</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>body7677@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1388-7681</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodyengineers_kr</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1442</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2045</v>
+      </c>
+      <c r="R52" t="n">
+        <v>3487</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1961345457</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1961345457</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>동경헬스클럽</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>wpdldoswl50@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>053-355-7888</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산남로 170</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wpdldoswl50</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>80</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>37405427</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37405427</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>매드짐</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>csd828282@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 연경지묘로 6 센텀타워 8층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/csd828282</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>14</v>
+      </c>
+      <c r="R54" t="n">
+        <v>32</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1036138674</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1036138674</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>올리브휘트니스사우나</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>koolerk@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>070-7739-6533</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정로 50 5층 여탕, 6층 남탕, 7층 헬스장</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_BqUGs</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>11</v>
+      </c>
+      <c r="R55" t="n">
+        <v>144</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>13473708</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13473708</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>깐부짐</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sukru20@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1361-3929</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 150 대현빌딩 6층 깐부짐</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>10</v>
+      </c>
+      <c r="R56" t="n">
+        <v>25</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1466260872</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1466260872</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>패러다임짐 칠곡동천점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>paradigm_cg@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1379-5157</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동천로23길 6-1 2층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/paradigm_cg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>317</v>
+      </c>
+      <c r="R57" t="n">
+        <v>425</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1005890243</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1005890243</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>이지피트니스</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>easyfitness01@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1350-1029</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/easyfitness01</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>605</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>286</v>
+      </c>
+      <c r="R58" t="n">
+        <v>891</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1129757069</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129757069</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>용천헬스</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dyd8310@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>053-954-7209</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 산격로 18</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>6</v>
+      </c>
+      <c r="R59" t="n">
+        <v>15</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>16131647</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16131647</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>발리헬스</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ybj063728@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1374-2209</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 구암로 153 동천빌딩 5,6층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ybj063728</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>445</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>446</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>16081155</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16081155</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>하이파이브짐 칠성점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>highfivegymmm@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1410-7641</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 옥산로17길 14 리치프라자 2층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/highfivegymmm</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>811</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>506</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1317</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>36929463</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36929463</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>스프라우트핏 여성전용 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>sproutfit_@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1402-8161</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동천로23길 10 4층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_Kpyxin?fbclid</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>116</v>
+      </c>
+      <c r="R62" t="n">
+        <v>203</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2039687494</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2039687494</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>위PT샵</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sdfgg110@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1380-4960</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동천로23길 6 루가빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yeba_2017ms.korea</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>15</v>
+      </c>
+      <c r="R63" t="n">
+        <v>109</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1564094440</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1564094440</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>빅토리짐 운동센터</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sjsjfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>053-325-8334</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정로106길 18 2F 유산소 및 요가룸 3F 웨이트존</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/victorygymofficial_</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>478</v>
+      </c>
+      <c r="R64" t="n">
+        <v>711</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1000816206</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1000816206</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>피트파크짐 PT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>seu0112@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1349-8265</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 168 엠브로타워 4층 407호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitparkgym?igsh=MzRlODBiNWFlZA==</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>150</v>
+      </c>
+      <c r="R65" t="n">
+        <v>197</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1036478329</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1036478329</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>스톤짐 복현점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>stonegym_3@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1333-5469</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_pQdrxj</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>712</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>174</v>
+      </c>
+      <c r="R66" t="n">
+        <v>886</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1113466448</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1113466448</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>바름PT&amp;피트니스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>baruemy@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1326-9724</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 연경중앙로3길 21 라온하제 8층(1층에 CU있어요)</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/baruemy/224250926219</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>252</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>118</v>
+      </c>
+      <c r="R67" t="n">
+        <v>370</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1848126055</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1848126055</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>밸런스핏 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>balancefit_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1356-4983</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 162-8 3층 밸런스핏</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_QIETxj/chat</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>112</v>
+      </c>
+      <c r="R68" t="n">
+        <v>176</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1569503169</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1569503169</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>벨루스FIT&amp;PT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>tizn_@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1439-2551</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동화천로 245 6층 604호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tizn_</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>57</v>
+      </c>
+      <c r="R69" t="n">
+        <v>102</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2076585284</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2076585284</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>로이짐 1:1 PT 침산점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ejhis12@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1426-1060</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산남로 157 4층 로이짐</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ejhis12</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>438</v>
+      </c>
+      <c r="R70" t="n">
+        <v>611</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1637712306</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1637712306</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>태고리즘 운동센터</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>gwgtaegorism@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1471-1283</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정로 551-50 4층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/taegorism_rehab/</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>107</v>
+      </c>
+      <c r="R71" t="n">
+        <v>154</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1942933824</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1942933824</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>국민피티 침산점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kukminpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1398-9797</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kukminpt</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>701</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1008</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1709</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1636758988</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1636758988</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>인스타퍼스널트레이닝 PT 침산점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>instarpt2019@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1345-9210</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산남로 165 5층 인스타퍼스널트레이닝 PT 침산점</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/instarpt2019</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>599</v>
+      </c>
+      <c r="R73" t="n">
+        <v>789</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1174523938</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1174523938</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>더모스트핏</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>themostfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1323-4262</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 173 시그니처타워 7층 더모스트핏</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/themostfit_hyun</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>24</v>
+      </c>
+      <c r="R74" t="n">
+        <v>36</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1092605247</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1092605247</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>비티비에스 PT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>whgudfo64@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1392-3331</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산남로 172 6층 비티비에스</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/whgudfo64</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>322</v>
+      </c>
+      <c r="R75" t="n">
+        <v>570</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1999844382</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1999844382</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>크로스핏마즈</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>zx95888@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1311-3298</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 144 화성투엠A동 지하1층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/marztraining</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>468</v>
+      </c>
+      <c r="R76" t="n">
+        <v>574</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>35720026</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35720026</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/북구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/북구_헬스장.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>웰니스 피트니스</t>
+          <t>써니짐 침산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pingdi@naver.com</t>
+          <t>cheyeong_007@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1384-1311</t>
+          <t>053-341-1588</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 475 3층</t>
+          <t>대구광역시 북구 침산남로 96 501호 502호 503호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sunnygym_official</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1392</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>169</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>1561</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1044132328</t>
+          <t>1534903715</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044132328</t>
+          <t>https://m.place.naver.com/place/1534903715</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>욱스짐 도남점 헬스PT</t>
+          <t>지젤 노원점 헬스 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thenamja89@naver.com</t>
+          <t>giselle331709@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1329-3354</t>
+          <t>0507-1342-7936</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로8길 1 시그니쳐타워 7층 욱스짐</t>
+          <t>대구광역시 북구 팔달로35길 20 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wook_s_gym</t>
+          <t>https://blog.naver.com/giselle331709</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>752</v>
+        <v>474</v>
       </c>
       <c r="Q3" t="n">
-        <v>218</v>
+        <v>494</v>
       </c>
       <c r="R3" t="n">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1340689579</t>
+          <t>1294730549</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340689579</t>
+          <t>https://m.place.naver.com/place/1294730549</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>원나인피트니스</t>
+          <t>마인드휘트니스 도남점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fhdnzlr892@naver.com</t>
+          <t>mindfitness21@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1800-6672</t>
+          <t>0507-1490-0792</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호암로 6 5층</t>
+          <t>대구광역시 북구 도남중앙로7길 20-4 601호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fhdnzlr892</t>
+          <t>https://blog.naver.com/mindfitness21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>194</v>
+        <v>824</v>
       </c>
       <c r="Q4" t="n">
-        <v>606</v>
+        <v>252</v>
       </c>
       <c r="R4" t="n">
-        <v>800</v>
+        <v>1076</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1696346241</t>
+          <t>1552558325</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696346241</t>
+          <t>https://m.place.naver.com/place/1552558325</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FM피트니스 동천점</t>
+          <t>피터짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>teran0120@naver.com</t>
+          <t>fitter_gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1472-9699</t>
+          <t>0507-1381-8120</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로 90 4층,5층</t>
+          <t>대구광역시 북구 옥산로 95 5층, 피터짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fm_fitness96</t>
+          <t>https://www.instagram.com/fitter__gym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>245</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="R5" t="n">
-        <v>63</v>
+        <v>442</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1811078908</t>
+          <t>1819328004</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1811078908</t>
+          <t>https://m.place.naver.com/place/1819328004</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>포레스트짐 헬스&amp;PT</t>
+          <t>데일리짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>forestgym-@naver.com</t>
+          <t>zhqlqudrl@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1482-0831</t>
+          <t>0507-1341-8555</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 43 2층</t>
+          <t>대구광역시 북구 침산로 158 건영하이츠 상가 (CU편의점 2층)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestgym_/</t>
+          <t>http://pf.kakao.com/_xmwltb</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>294</v>
       </c>
       <c r="R6" t="n">
-        <v>40</v>
+        <v>491</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1186829756</t>
+          <t>20771266</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186829756</t>
+          <t>https://m.place.naver.com/place/20771266</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,25 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레드워크아웃 헬스 &amp; PT</t>
+          <t>태양헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>siytg1234@naver.com</t>
+          <t>dnrlek78@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>053-324-1236</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로 127 4층,5층 레드워크아웃 (성화여고건너, 봄봄 건물)</t>
+          <t>대구광역시 북구 칠곡중앙대로 423 태양헬스 9층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/siytg1234</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,12 +1066,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1083,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>255</v>
+        <v>48</v>
       </c>
       <c r="Q7" t="n">
-        <v>241</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>496</v>
+        <v>53</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1179762159</t>
+          <t>37992328</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179762159</t>
+          <t>https://m.place.naver.com/place/37992328</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>어바웃더핏 헬스 &amp; PT</t>
+          <t>빅토리짐 PT&amp;헬스 동천점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mildodrax2@naver.com</t>
+          <t>sjsjfit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1314-2445</t>
+          <t>0507-1370-1301</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 149 태전동 1195 번지 4층, 어바웃더핏</t>
+          <t>대구광역시 북구 동천로23길 36 2층 201호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aboutthefit_gym</t>
+          <t>https://blog.naver.com/sjsjfit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1161,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1172,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>767</v>
+        <v>102</v>
       </c>
       <c r="Q8" t="n">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="R8" t="n">
-        <v>904</v>
+        <v>292</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1258524487</t>
+          <t>1903714032</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258524487</t>
+          <t>https://m.place.naver.com/place/1903714032</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1218,25 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더레드짐 헬스 &amp; PT</t>
+          <t>원나인피트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>thered_gym@naver.com</t>
+          <t>fhdnzlr892@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1800-6672</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로 105 태왕아너스상가 4층, 5층</t>
+          <t>대구광역시 북구 호암로 6 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theredgym</t>
+          <t>https://blog.naver.com/fhdnzlr892</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1251,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>472</v>
+        <v>194</v>
       </c>
       <c r="Q9" t="n">
-        <v>159</v>
+        <v>606</v>
       </c>
       <c r="R9" t="n">
-        <v>631</v>
+        <v>800</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1243559985</t>
+          <t>1696346241</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243559985</t>
+          <t>https://m.place.naver.com/place/1696346241</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>그린짐</t>
+          <t>팀에스핏</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pk0236@naver.com</t>
+          <t>moa0121moa@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1390-5563</t>
+          <t>0507-1414-7988</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 439 502호</t>
+          <t>대구광역시 북구 동북로 280 3,4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hee_moa0121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1340,7 +1348,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1361,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="R10" t="n">
-        <v>28</v>
+        <v>203</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1007068851</t>
+          <t>38258053</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1007068851</t>
+          <t>https://m.place.naver.com/place/38258053</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1410,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>팀에스핏</t>
+          <t>매드짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>moa0121moa@naver.com</t>
+          <t>csd828282@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1414-7988</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 280 3,4층</t>
+          <t>대구광역시 북구 연경지묘로 6 센텀타워 8층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hee_moa0121</t>
+          <t>https://blog.naver.com/csd828282</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1439,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>202</v>
+        <v>32</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38258053</t>
+          <t>1036138674</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38258053</t>
+          <t>https://m.place.naver.com/place/1036138674</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1500,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>팀42</t>
+          <t>패러다임짐 칠곡동천점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sun0799dh@naver.com</t>
+          <t>paradigm_cg@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1306-2047</t>
+          <t>0507-1379-5157</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 북구 원대로 76 지하1층</t>
+          <t>대구광역시 북구 동천로23길 6-1 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/paradigm_cg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1528,12 +1532,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1549,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>317</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>426</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1878169203</t>
+          <t>1005890243</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1878169203</t>
+          <t>https://m.place.naver.com/place/1005890243</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>버거짐</t>
+          <t>아이디짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>burgergym@naver.com</t>
+          <t>ildomin@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1400-9556</t>
+          <t>0507-1319-9446</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로 209 1층</t>
+          <t>대구광역시 북구 내곡로 73 금강프라자 3층 아이디헬스IDGYM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/burger_gym_</t>
+          <t>https://www.instagram.com/idgym24h?igsh=MTBnOHl0a2M3enBxdQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1638,7 +1642,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1647,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>155</v>
+        <v>74</v>
       </c>
       <c r="Q13" t="n">
-        <v>362</v>
+        <v>136</v>
       </c>
       <c r="R13" t="n">
-        <v>517</v>
+        <v>210</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1590239180</t>
+          <t>1254581921</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1590239180</t>
+          <t>https://m.place.naver.com/place/1254581921</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1688,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>태양헬스</t>
+          <t>하이파이브짐 칠성점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dnrlek78@naver.com</t>
+          <t>highfivegymmm@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>053-324-1236</t>
+          <t>0507-1410-7641</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 423 태양헬스 9층</t>
+          <t>대구광역시 북구 옥산로17길 14 리치프라자 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/highfivegymmm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1716,12 +1720,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1737,17 +1741,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>48</v>
+        <v>811</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>507</v>
       </c>
       <c r="R14" t="n">
-        <v>53</v>
+        <v>1318</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>37992328</t>
+          <t>36929463</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37992328</t>
+          <t>https://m.place.naver.com/place/36929463</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1778,25 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>리브</t>
+          <t>버거짐</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ekgus1002@naver.com</t>
+          <t>burgergym@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1400-9556</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 180-6 지하1층</t>
+          <t>대구광역시 북구 팔달로 209 1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lib_official_/</t>
+          <t>https://www.instagram.com/burger_gym_</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1831,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>365</v>
       </c>
       <c r="R15" t="n">
-        <v>23</v>
+        <v>520</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2045901558</t>
+          <t>1590239180</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045901558</t>
+          <t>https://m.place.naver.com/place/1590239180</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1868,29 +1876,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>더퍼스트 피트니스 칠곡점</t>
+          <t>웰니스 피트니스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>tffpceo10@naver.com</t>
+          <t>monthlypeople@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1304-3714</t>
+          <t>0507-1384-1311</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 125 5층</t>
+          <t>대구광역시 북구 칠곡중앙대로 475 3층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tffpceo10</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1900,12 +1908,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1921,17 +1929,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>308</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>280</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>588</v>
+        <v>5</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1040934279</t>
+          <t>1044132328</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040934279</t>
+          <t>https://m.place.naver.com/place/1044132328</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1962,29 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>바디채널 침산점</t>
+          <t>조지아 헬스 PT 스피닝 GX 칠곡점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bodycs@naver.com</t>
+          <t>gogia4879@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1342-4850</t>
+          <t>0507-1383-4879</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 154 10층</t>
+          <t>대구광역시 북구 동천로 133 701호,702호,703호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_chimsan</t>
+          <t>https://www.instagram.com/georgia.one1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2019,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="Q17" t="n">
-        <v>1529</v>
+        <v>446</v>
       </c>
       <c r="R17" t="n">
-        <v>1706</v>
+        <v>720</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1023076989</t>
+          <t>1013813873</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023076989</t>
+          <t>https://m.place.naver.com/place/1013813873</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2056,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>지젤 노원점 헬스 PT</t>
+          <t>FM피트니스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>giselle331709@naver.com</t>
+          <t>teran0120@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1342-7936</t>
+          <t>0507-1326-7507</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로35길 20 5층</t>
+          <t>대구광역시 북구 팔거천동로 80-1 태백빌딩 6층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/giselle331709</t>
+          <t>https://blog.naver.com/teran0120</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2113,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>475</v>
+        <v>52</v>
       </c>
       <c r="Q18" t="n">
-        <v>493</v>
+        <v>111</v>
       </c>
       <c r="R18" t="n">
-        <v>968</v>
+        <v>163</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1294730549</t>
+          <t>1115611185</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294730549</t>
+          <t>https://m.place.naver.com/place/1115611185</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2150,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FM피트니스 태전점</t>
+          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>werxman@naver.com</t>
+          <t>body7677@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1336-9688</t>
+          <t>0507-1388-7681</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 269 4층</t>
+          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fmfitness9696</t>
+          <t>https://www.instagram.com/bodyengineers_kr</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2207,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>58</v>
+        <v>1442</v>
       </c>
       <c r="Q19" t="n">
-        <v>129</v>
+        <v>2054</v>
       </c>
       <c r="R19" t="n">
-        <v>187</v>
+        <v>3496</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1649195059</t>
+          <t>1961345457</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1649195059</t>
+          <t>https://m.place.naver.com/place/1961345457</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>써니짐 침산점</t>
+          <t>패러다임짐 복현점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cheyeong_007@naver.com</t>
+          <t>paradigm1378@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>053-341-1588</t>
+          <t>0507-1346-1460</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 96 501호 502호 503호</t>
+          <t>대구광역시 북구 동북로 223 3층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunnygym_official</t>
+          <t>https://blog.naver.com/paradigm1378/223060126537</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2281,7 +2289,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2301,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1392</v>
+        <v>376</v>
       </c>
       <c r="Q20" t="n">
-        <v>169</v>
+        <v>380</v>
       </c>
       <c r="R20" t="n">
-        <v>1561</v>
+        <v>756</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1534903715</t>
+          <t>1397098871</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1534903715</t>
+          <t>https://m.place.naver.com/place/1397098871</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2338,29 +2346,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>탑클래스짐 서변점</t>
+          <t>FM피트니스 동천점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>topclass_gym@naver.com</t>
+          <t>teran0120@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1393-3466</t>
+          <t>0507-1472-9699</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로 227 5층</t>
+          <t>대구광역시 북구 대천로 90 4층,5층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/topclass_gym</t>
+          <t>https://www.instagram.com/fm_fitness96</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2375,7 +2383,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2395,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>225</v>
+        <v>23</v>
       </c>
       <c r="Q21" t="n">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="R21" t="n">
-        <v>390</v>
+        <v>63</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1042649945</t>
+          <t>1811078908</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1042649945</t>
+          <t>https://m.place.naver.com/place/1811078908</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2440,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아이디짐 헬스&amp;PT</t>
+          <t>브이피트니스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ildomin@naver.com</t>
+          <t>vfitness3650@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1319-9446</t>
+          <t>0507-1461-3654</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 북구 내곡로 73 금강프라자 3층 아이디헬스IDGYM</t>
+          <t>대구광역시 북구 매전로 80 , 3층 301호(태전동)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/idgym24h?igsh=MTBnOHl0a2M3enBxdQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/vfitness3650</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2480,7 +2488,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2489,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="Q22" t="n">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="R22" t="n">
-        <v>209</v>
+        <v>63</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2512,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1254581921</t>
+          <t>1866227499</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1254581921</t>
+          <t>https://m.place.naver.com/place/1866227499</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2526,29 +2534,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>바디웨이 헬스&amp;PT</t>
+          <t>칠성휘트니스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>striver_ocean@naver.com</t>
+          <t>ukino2339@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1488-2098</t>
+          <t>0507-1489-2039</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로 148 4, 5층</t>
+          <t>대구광역시 북구 칠성남로 101 101동</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/striver_ocean</t>
+          <t>https://www.instagram.com/7sung_f</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2563,7 +2571,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2579,17 +2587,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="R23" t="n">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2606,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1534494580</t>
+          <t>1198192231</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1534494580</t>
+          <t>https://m.place.naver.com/place/1198192231</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2620,29 +2628,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>엔드짐</t>
+          <t>피트온24 칠곡점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>himy491@naver.com</t>
+          <t>fitness240@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>053-311-6939</t>
+          <t>053-313-8817</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매천로18길 29 5층, 엔드짐</t>
+          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/endgym_official</t>
+          <t>https://blog.naver.com/fitness240</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2657,7 +2665,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2668,7 +2676,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2677,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>29</v>
+        <v>2311</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>976</v>
       </c>
       <c r="R24" t="n">
-        <v>43</v>
+        <v>3287</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2700,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1314145805</t>
+          <t>1175448883</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314145805</t>
+          <t>https://m.place.naver.com/place/1175448883</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2714,29 +2722,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>피터짐</t>
+          <t>어바웃더핏 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fitter_gym@naver.com</t>
+          <t>mildodrax2@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1381-8120</t>
+          <t>0507-1314-2445</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로 95 5층, 피터짐</t>
+          <t>대구광역시 북구 학정로 149 태전동 1195 번지 4층, 어바웃더핏</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitter__gym</t>
+          <t>https://www.instagram.com/aboutthefit_gym</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2762,7 +2770,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2771,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>244</v>
+        <v>773</v>
       </c>
       <c r="Q25" t="n">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="R25" t="n">
-        <v>439</v>
+        <v>910</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1819328004</t>
+          <t>1258524487</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1819328004</t>
+          <t>https://m.place.naver.com/place/1258524487</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2808,29 +2816,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>마인드휘트니스 도남점</t>
+          <t>헬스보이짐 롯데대구역점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mindfitness21@naver.com</t>
+          <t>healthboygym86@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1490-0792</t>
+          <t>0507-1439-0444</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로7길 20-4 601호</t>
+          <t>대구광역시 북구 태평로 161 9층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness21</t>
+          <t>https://www.instagram.com/healthboy86</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2845,7 +2853,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2865,13 +2873,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>823</v>
+        <v>442</v>
       </c>
       <c r="Q26" t="n">
-        <v>251</v>
+        <v>149</v>
       </c>
       <c r="R26" t="n">
-        <v>1074</v>
+        <v>591</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1552558325</t>
+          <t>1966515992</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1552558325</t>
+          <t>https://m.place.naver.com/place/1966515992</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2902,34 +2910,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>스타트짐</t>
+          <t>올리브휘트니스사우나</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ajfitness6262@naver.com</t>
+          <t>koolerk@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1457-6260</t>
+          <t>070-7739-6533</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현로 84 (농협건물) 3층</t>
+          <t>대구광역시 북구 학정로 50 5층 여탕, 6층 남탕, 7층 헬스장</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ajfitness6262</t>
+          <t>http://pf.kakao.com/_BqUGs</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2939,7 +2947,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2950,22 +2958,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="Q27" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="R27" t="n">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>32693542</t>
+          <t>13473708</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32693542</t>
+          <t>https://m.place.naver.com/place/13473708</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2996,34 +3004,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>스카이짐</t>
+          <t>스프라우트핏 여성전용 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>pyup2000@naver.com</t>
+          <t>sproutfit_@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1432-9697</t>
+          <t>0507-1402-8161</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학남로 95 2층 스카이짐</t>
+          <t>대구광역시 북구 동천로23길 10 4층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pyup2000</t>
+          <t>https://pf.kakao.com/_Kpyxin?fbclid</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3033,7 +3041,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3044,22 +3052,22 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="Q28" t="n">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="R28" t="n">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3076,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>60630663</t>
+          <t>2039687494</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60630663</t>
+          <t>https://m.place.naver.com/place/2039687494</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3090,29 +3098,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스카이휘트니스 사우나</t>
+          <t>FM피트니스 태전점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>uvtt0407@naver.com</t>
+          <t>werxman@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>053-956-8500</t>
+          <t>0507-1336-9688</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 156 5층헬스장</t>
+          <t>대구광역시 북구 칠곡중앙대로 269 4층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/fmfitness9696</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3122,7 +3130,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3143,17 +3151,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="R29" t="n">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3170,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1560224728</t>
+          <t>1649195059</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1560224728</t>
+          <t>https://m.place.naver.com/place/1649195059</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3184,39 +3192,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>데일리짐</t>
+          <t>용천헬스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>zhqlqudrl@naver.com</t>
+          <t>dyd8310@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1341-8555</t>
+          <t>053-954-7209</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 158 건영하이츠 상가 (CU편의점 2층)</t>
+          <t>대구광역시 북구 산격로 18</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xmwltb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3232,22 +3240,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>294</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>491</v>
+        <v>15</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3264,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20771266</t>
+          <t>16131647</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20771266</t>
+          <t>https://m.place.naver.com/place/16131647</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3278,39 +3286,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>레드짐 복현오거리점 헬스 &amp; PT</t>
+          <t>깐부짐</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>redgym8555@naver.com</t>
+          <t>sukru20@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>053-1877-3632</t>
+          <t>0507-1361-3929</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 북구 검단로 9 3층, 4층</t>
+          <t>대구광역시 북구 동북로 150 대현빌딩 6층 깐부짐</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://litt.ly/redgym_b5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3331,17 +3339,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>815</v>
+        <v>15</v>
       </c>
       <c r="Q31" t="n">
-        <v>662</v>
+        <v>10</v>
       </c>
       <c r="R31" t="n">
-        <v>1477</v>
+        <v>25</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,56 +3358,56 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1813814971</t>
+          <t>1466260872</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813814971</t>
+          <t>https://m.place.naver.com/place/1466260872</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>칠성휘트니스</t>
+          <t>오짐 헬스&amp;PT 동천점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ukino2339@naver.com</t>
+          <t>forever7582@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1489-2039</t>
+          <t>0507-1421-9655</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 101 101동</t>
+          <t>대구광역시 북구 동천로 125-4 4층 오짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/7sung_f</t>
+          <t>https://m.site.naver.com/1CMKz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3429,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>307</v>
       </c>
       <c r="Q32" t="n">
-        <v>24</v>
+        <v>657</v>
       </c>
       <c r="R32" t="n">
-        <v>27</v>
+        <v>964</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3452,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1198192231</t>
+          <t>1264751882</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198192231</t>
+          <t>https://m.place.naver.com/place/1264751882</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3474,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>피트온24 복현점</t>
+          <t>원나인피트니스 침산점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mave000@naver.com</t>
+          <t>oneninegym_chimsan@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1322-3225</t>
+          <t>1800-9533</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
+          <t>대구광역시 북구 침산남로 96 2층 201호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mave000</t>
+          <t>https://blog.naver.com/oneninegym_chimsan</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3523,13 +3531,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2020</v>
+        <v>219</v>
       </c>
       <c r="Q33" t="n">
-        <v>980</v>
+        <v>135</v>
       </c>
       <c r="R33" t="n">
-        <v>3000</v>
+        <v>354</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,17 +3546,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1855565865</t>
+          <t>1682965261</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855565865</t>
+          <t>https://m.place.naver.com/place/1682965261</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3560,25 +3568,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>트라이핏 복현푸르지오점</t>
+          <t>월드짐 피트니스 센터</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>trifit4@naver.com</t>
+          <t>worldgym_cs@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>053-356-3600</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 325 3, 4층</t>
+          <t>대구광역시 북구 침산로 142</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/trifit_bokhyeon</t>
+          <t>https://blog.naver.com/worldgym_cs</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3593,7 +3605,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3613,13 +3625,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="Q34" t="n">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="R34" t="n">
-        <v>271</v>
+        <v>89</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,17 +3640,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1875195371</t>
+          <t>1802720489</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875195371</t>
+          <t>https://m.place.naver.com/place/1802720489</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3650,29 +3662,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FM피트니스</t>
+          <t>탑클래스짐 서변점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>teran0120@naver.com</t>
+          <t>topclass_gym@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1326-7507</t>
+          <t>0507-1393-3466</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로 80-1 태백빌딩 6층</t>
+          <t>대구광역시 북구 호국로 227 5층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teran0120</t>
+          <t>https://blog.naver.com/topclass_gym</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3707,13 +3719,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>52</v>
+        <v>226</v>
       </c>
       <c r="Q35" t="n">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="R35" t="n">
-        <v>163</v>
+        <v>391</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,56 +3734,56 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1115611185</t>
+          <t>1042649945</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1115611185</t>
+          <t>https://m.place.naver.com/place/1042649945</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>오짐 헬스&amp;PT 동천점</t>
+          <t>욱스짐 도남점 헬스PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>forever7582@naver.com</t>
+          <t>thenamja89@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1421-9655</t>
+          <t>0507-1329-3354</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 125-4 4층 오짐 헬스&amp;PT</t>
+          <t>대구광역시 북구 도남중앙로8길 1 시그니쳐타워 7층 욱스짐</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://m.site.naver.com/1CMKz</t>
+          <t>https://www.instagram.com/wook_s_gym</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3801,13 +3813,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>307</v>
+        <v>756</v>
       </c>
       <c r="Q36" t="n">
-        <v>657</v>
+        <v>221</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>977</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,17 +3828,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1264751882</t>
+          <t>1340689579</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264751882</t>
+          <t>https://m.place.naver.com/place/1340689579</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3838,29 +3850,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>맥시멈짐</t>
+          <t>스카이휘트니스 사우나</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>maximum_si@naver.com</t>
+          <t>uvtt0407@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1310-3561</t>
+          <t>053-956-8500</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현로 102 삼주빌딩 5층</t>
+          <t>대구광역시 북구 동북로 156 5층헬스장</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/leetaekwan_classic</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3870,7 +3882,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3891,17 +3903,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="Q37" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,17 +3922,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1928149032</t>
+          <t>1560224728</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928149032</t>
+          <t>https://m.place.naver.com/place/1560224728</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3932,29 +3944,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>크로스핏타임 칠곡점</t>
+          <t>바디채널 침산점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>timegym2021@naver.com</t>
+          <t>bodycs@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1355-3967</t>
+          <t>0507-1342-4850</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로 224 지하1층</t>
+          <t>대구광역시 북구 침산남로 154 10층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/shs4uWwf</t>
+          <t>https://www.instagram.com/bodychannel_chimsan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3980,7 +3992,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3989,13 +4001,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>69</v>
+        <v>177</v>
       </c>
       <c r="Q38" t="n">
-        <v>37</v>
+        <v>1529</v>
       </c>
       <c r="R38" t="n">
-        <v>106</v>
+        <v>1706</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4004,17 +4016,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1151810571</t>
+          <t>1023076989</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1151810571</t>
+          <t>https://m.place.naver.com/place/1023076989</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4026,25 +4038,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>제로짐 복현</t>
+          <t>레드짐 침산점 헬스&amp;스파</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>zerogym_@naver.com</t>
+          <t>redgym-chim@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1329-5605</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 291 4층 제로짐</t>
+          <t>대구광역시 북구 침산로 138 6층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zerogym__</t>
+          <t>https://www.instagram.com/redgym_chimsan</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4079,13 +4095,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>36</v>
+        <v>394</v>
       </c>
       <c r="Q39" t="n">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="R39" t="n">
-        <v>67</v>
+        <v>619</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4094,17 +4110,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2083396096</t>
+          <t>1070126824</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2083396096</t>
+          <t>https://m.place.naver.com/place/1070126824</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4116,29 +4132,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>조지아 헬스 PT 스피닝 GX 칠곡점</t>
+          <t>그린짐</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>gogia4879@naver.com</t>
+          <t>pk0236@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1383-4879</t>
+          <t>0507-1390-5563</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 133 701호,702호,703호</t>
+          <t>대구광역시 북구 학정로 439 502호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/georgia.one1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4148,7 +4164,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4169,17 +4185,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>273</v>
+        <v>23</v>
       </c>
       <c r="Q40" t="n">
-        <v>446</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>719</v>
+        <v>28</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4188,17 +4204,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1013813873</t>
+          <t>1007068851</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013813873</t>
+          <t>https://m.place.naver.com/place/1007068851</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4210,29 +4226,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>심피트니스</t>
+          <t>제로짐 복현</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>simfitness24@naver.com</t>
+          <t>zerogym_@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1483-1279</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 북구 공항로 69-9 69-11, 외 2필지</t>
+          <t>대구광역시 북구 동북로 291 4층 제로짐</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/simfitness24</t>
+          <t>https://www.instagram.com/zerogym__</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,7 +4259,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4267,13 +4279,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>324</v>
+        <v>35</v>
       </c>
       <c r="Q41" t="n">
-        <v>452</v>
+        <v>32</v>
       </c>
       <c r="R41" t="n">
-        <v>776</v>
+        <v>67</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4282,17 +4294,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1569924819</t>
+          <t>2083396096</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569924819</t>
+          <t>https://m.place.naver.com/place/2083396096</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4304,29 +4316,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>원나인피트니스 침산점</t>
+          <t>맥시멈짐</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>oneninegym_chimsan@naver.com</t>
+          <t>maximum_si@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1800-9533</t>
+          <t>0507-1310-3561</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 96 2층 201호</t>
+          <t>대구광역시 북구 대현로 102 삼주빌딩 5층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oneninegym_chimsan</t>
+          <t>https://www.instagram.com/leetaekwan_classic</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4341,7 +4353,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4361,13 +4373,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>219</v>
+        <v>24</v>
       </c>
       <c r="Q42" t="n">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="R42" t="n">
-        <v>354</v>
+        <v>89</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4376,17 +4388,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1682965261</t>
+          <t>1928149032</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682965261</t>
+          <t>https://m.place.naver.com/place/1928149032</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4398,29 +4410,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>지젤 칠곡점 헬스 PT GX 요가</t>
+          <t>스타트짐</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>giselle331704@naver.com</t>
+          <t>ajfitness6262@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1321-6496</t>
+          <t>0507-1457-6260</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동암로 90 3층</t>
+          <t>대구광역시 북구 대현로 84 (농협건물) 3층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+          <t>https://blog.naver.com/ajfitness6262</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4435,7 +4447,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4451,17 +4463,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1241</v>
+        <v>149</v>
       </c>
       <c r="Q43" t="n">
-        <v>544</v>
+        <v>34</v>
       </c>
       <c r="R43" t="n">
-        <v>1785</v>
+        <v>183</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4470,17 +4482,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1616049160</t>
+          <t>32693542</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616049160</t>
+          <t>https://m.place.naver.com/place/32693542</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4492,29 +4504,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>월드짐 피트니스 센터</t>
+          <t>스카이짐</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>worldgym_cs@naver.com</t>
+          <t>pyup2000@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>053-356-3600</t>
+          <t>0507-1432-9697</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 142</t>
+          <t>대구광역시 북구 학남로 95 2층 스카이짐</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/worldgym_cs</t>
+          <t>https://blog.naver.com/pyup2000</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4545,17 +4557,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q44" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="R44" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4564,17 +4576,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1802720489</t>
+          <t>60630663</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802720489</t>
+          <t>https://m.place.naver.com/place/60630663</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4586,29 +4598,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>레드짐 침산점 헬스&amp;스파</t>
+          <t>심피트니스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>redgym-chim@naver.com</t>
+          <t>simfitness24@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1329-5605</t>
+          <t>0507-1483-1279</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 138 6층</t>
+          <t>대구광역시 북구 공항로 69-9 69-11, 외 2필지</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/redgym_chimsan</t>
+          <t>https://blog.naver.com/simfitness24</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4623,7 +4635,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4643,13 +4655,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>392</v>
+        <v>328</v>
       </c>
       <c r="Q45" t="n">
-        <v>224</v>
+        <v>453</v>
       </c>
       <c r="R45" t="n">
-        <v>616</v>
+        <v>781</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,17 +4670,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1070126824</t>
+          <t>1569924819</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070126824</t>
+          <t>https://m.place.naver.com/place/1569924819</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4680,34 +4692,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>패러다임짐 복현점</t>
+          <t>레드짐 복현오거리점 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>paradigm1378@naver.com</t>
+          <t>redgym8555@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1346-1460</t>
+          <t>053-1877-3632</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 223 3층</t>
+          <t>대구광역시 북구 검단로 9 3층, 4층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/paradigm1378/223060126537</t>
+          <t>https://litt.ly/redgym_b5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4717,7 +4729,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4737,13 +4749,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>376</v>
+        <v>815</v>
       </c>
       <c r="Q46" t="n">
-        <v>380</v>
+        <v>662</v>
       </c>
       <c r="R46" t="n">
-        <v>756</v>
+        <v>1477</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4752,17 +4764,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1397098871</t>
+          <t>1813814971</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397098871</t>
+          <t>https://m.place.naver.com/place/1813814971</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4774,29 +4786,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>나홀로짐</t>
+          <t>포레스트짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bs4376@naver.com</t>
+          <t>forestgym-@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>053-234-5678</t>
+          <t>0507-1482-0831</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동변로16길 8-8</t>
+          <t>대구광역시 북구 칠성남로 43 2층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://instagram.com/use_gym_alone?utm_medium=copy_link</t>
+          <t>https://www.instagram.com/forestgym_/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4831,13 +4843,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R47" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,51 +4858,47 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1237091070</t>
+          <t>1186829756</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1237091070</t>
+          <t>https://m.place.naver.com/place/1186829756</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>빅토리짐 PT&amp;헬스 동천점</t>
+          <t>더레드짐 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sjsjfit@naver.com</t>
+          <t>thered_gym@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1370-1301</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 36 2층 201호</t>
+          <t>대구광역시 북구 복현로 105 태왕아너스상가 4층, 5층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sjsjfit</t>
+          <t>https://www.instagram.com/theredgym</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4905,7 +4913,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4925,13 +4933,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>102</v>
+        <v>472</v>
       </c>
       <c r="Q48" t="n">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="R48" t="n">
-        <v>292</v>
+        <v>630</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4940,17 +4948,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1903714032</t>
+          <t>1243559985</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903714032</t>
+          <t>https://m.place.naver.com/place/1243559985</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4962,29 +4970,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>피트온24 칠곡점</t>
+          <t>엔드짐</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>fitness240@naver.com</t>
+          <t>himy491@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>053-313-8817</t>
+          <t>053-311-6939</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
+          <t>대구광역시 북구 매천로18길 29 5층, 엔드짐</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness240</t>
+          <t>https://www.instagram.com/endgym_official</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4999,7 +5007,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5010,7 +5018,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5019,13 +5027,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2309</v>
+        <v>29</v>
       </c>
       <c r="Q49" t="n">
-        <v>969</v>
+        <v>14</v>
       </c>
       <c r="R49" t="n">
-        <v>3278</v>
+        <v>43</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5034,17 +5042,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1175448883</t>
+          <t>1314145805</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1175448883</t>
+          <t>https://m.place.naver.com/place/1314145805</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5056,34 +5064,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>브이피트니스</t>
+          <t>크로스핏타임 칠곡점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>vfitness3650@naver.com</t>
+          <t>timegym2021@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1461-3654</t>
+          <t>0507-1355-3967</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로 80 , 3층 301호(태전동)</t>
+          <t>대구광역시 북구 팔거천동로 224 지하1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vfitness3650</t>
+          <t>https://open.kakao.com/o/shs4uWwf</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5104,7 +5112,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5113,13 +5121,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="R50" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5128,17 +5136,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1866227499</t>
+          <t>1151810571</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1866227499</t>
+          <t>https://m.place.naver.com/place/1151810571</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5150,29 +5158,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>헬스보이짐 롯데대구역점</t>
+          <t>레드워크아웃 헬스 &amp; PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>healthboygym86@naver.com</t>
+          <t>siytg1234@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1439-0444</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태평로 161 9층</t>
+          <t>대구광역시 북구 복현로 127 4층,5층 레드워크아웃 (성화여고건너, 봄봄 건물)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy86</t>
+          <t>https://blog.naver.com/siytg1234</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5187,7 +5191,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5207,13 +5211,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>441</v>
+        <v>255</v>
       </c>
       <c r="Q51" t="n">
-        <v>148</v>
+        <v>241</v>
       </c>
       <c r="R51" t="n">
-        <v>589</v>
+        <v>496</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5222,17 +5226,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1966515992</t>
+          <t>1179762159</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966515992</t>
+          <t>https://m.place.naver.com/place/1179762159</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5244,29 +5248,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+          <t>트라이핏 복현푸르지오점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>body7677@naver.com</t>
+          <t>trifit4@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1388-7681</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+          <t>대구광역시 북구 동북로 325 3, 4층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyengineers_kr</t>
+          <t>https://www.instagram.com/trifit_bokhyeon</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1442</v>
+        <v>115</v>
       </c>
       <c r="Q52" t="n">
-        <v>2045</v>
+        <v>157</v>
       </c>
       <c r="R52" t="n">
-        <v>3487</v>
+        <v>272</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5316,17 +5316,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1961345457</t>
+          <t>1875195371</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961345457</t>
+          <t>https://m.place.naver.com/place/1875195371</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5338,29 +5338,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>동경헬스클럽</t>
+          <t>피트온24 복현점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>wpdldoswl50@naver.com</t>
+          <t>mave000@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>053-355-7888</t>
+          <t>0507-1322-3225</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 170</t>
+          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wpdldoswl50</t>
+          <t>https://blog.naver.com/mave000</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5391,17 +5391,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>76</v>
+        <v>2022</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>983</v>
       </c>
       <c r="R53" t="n">
-        <v>80</v>
+        <v>3005</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5410,17 +5410,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>37405427</t>
+          <t>1855565865</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37405427</t>
+          <t>https://m.place.naver.com/place/1855565865</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5432,25 +5432,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>매드짐</t>
+          <t>더퍼스트 피트니스 칠곡점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>csd828282@naver.com</t>
+          <t>tffpceo10@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1304-3714</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경지묘로 6 센텀타워 8층</t>
+          <t>대구광역시 북구 동천로 125 5층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/csd828282</t>
+          <t>https://blog.naver.com/tffpceo10</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5485,13 +5489,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>18</v>
+        <v>309</v>
       </c>
       <c r="Q54" t="n">
-        <v>14</v>
+        <v>278</v>
       </c>
       <c r="R54" t="n">
-        <v>32</v>
+        <v>587</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,17 +5504,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1036138674</t>
+          <t>1040934279</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036138674</t>
+          <t>https://m.place.naver.com/place/1040934279</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5522,34 +5526,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>올리브휘트니스사우나</t>
+          <t>이지피트니스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>koolerk@naver.com</t>
+          <t>easyfitness01@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>070-7739-6533</t>
+          <t>0507-1350-1029</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 50 5층 여탕, 6층 남탕, 7층 헬스장</t>
+          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_BqUGs</t>
+          <t>https://blog.naver.com/easyfitness01</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5559,7 +5563,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5570,7 +5574,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5579,13 +5583,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>133</v>
+        <v>604</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>286</v>
       </c>
       <c r="R55" t="n">
-        <v>144</v>
+        <v>890</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5594,17 +5598,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13473708</t>
+          <t>1129757069</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13473708</t>
+          <t>https://m.place.naver.com/place/1129757069</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5616,29 +5620,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>깐부짐</t>
+          <t>리브</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sukru20@naver.com</t>
+          <t>jm8335@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1361-3929</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 150 대현빌딩 6층 깐부짐</t>
+          <t>대구광역시 북구 침산남로 180-6 지하1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lib_official_/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5669,17 +5669,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,17 +5688,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1466260872</t>
+          <t>2045901558</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466260872</t>
+          <t>https://m.place.naver.com/place/2045901558</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5710,29 +5710,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>패러다임짐 칠곡동천점</t>
+          <t>바디웨이 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>paradigm_cg@naver.com</t>
+          <t>striver_ocean@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1379-5157</t>
+          <t>0507-1488-2098</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 6-1 2층</t>
+          <t>대구광역시 북구 구암로 148 4, 5층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/paradigm_cg</t>
+          <t>https://blog.naver.com/striver_ocean</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5763,17 +5763,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Q57" t="n">
-        <v>317</v>
+        <v>76</v>
       </c>
       <c r="R57" t="n">
-        <v>425</v>
+        <v>149</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5782,17 +5782,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1005890243</t>
+          <t>1534494580</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005890243</t>
+          <t>https://m.place.naver.com/place/1534494580</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5804,29 +5804,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>이지피트니스</t>
+          <t>팀42</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>easyfitness01@naver.com</t>
+          <t>sun0799dh@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1350-1029</t>
+          <t>0507-1306-2047</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
+          <t>대구광역시 북구 원대로 76 지하1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/easyfitness01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5857,17 +5857,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>605</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>286</v>
+        <v>11</v>
       </c>
       <c r="R58" t="n">
-        <v>891</v>
+        <v>11</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1129757069</t>
+          <t>1878169203</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129757069</t>
+          <t>https://m.place.naver.com/place/1878169203</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5898,29 +5898,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>용천헬스</t>
+          <t>지젤 칠곡점 헬스 PT GX 요가</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dyd8310@naver.com</t>
+          <t>giselle331704@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>053-954-7209</t>
+          <t>0507-1321-6496</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 북구 산격로 18</t>
+          <t>대구광역시 북구 동암로 90 3층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>9</v>
+        <v>1241</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>544</v>
       </c>
       <c r="R59" t="n">
-        <v>15</v>
+        <v>1785</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5970,17 +5970,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>16131647</t>
+          <t>1616049160</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16131647</t>
+          <t>https://m.place.naver.com/place/1616049160</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6074,46 +6074,46 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>하이파이브짐 칠성점</t>
+          <t>스톤짐 복현점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>highfivegymmm@naver.com</t>
+          <t>stonegym_3@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1410-7641</t>
+          <t>0507-1333-5469</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로17길 14 리치프라자 2층</t>
+          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/highfivegymmm</t>
+          <t>http://pf.kakao.com/_pQdrxj</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6134,7 +6134,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>811</v>
+        <v>714</v>
       </c>
       <c r="Q61" t="n">
-        <v>506</v>
+        <v>176</v>
       </c>
       <c r="R61" t="n">
-        <v>1317</v>
+        <v>890</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6158,56 +6158,56 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>36929463</t>
+          <t>1113466448</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36929463</t>
+          <t>https://m.place.naver.com/place/1113466448</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>스프라우트핏 여성전용 헬스&amp;PT</t>
+          <t>빅토리짐 운동센터</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sproutfit_@naver.com</t>
+          <t>sjsjfit@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1402-8161</t>
+          <t>053-325-8334</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 10 4층</t>
+          <t>대구광역시 북구 학정로106길 18 2F 유산소 및 요가룸 3F 웨이트존</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_Kpyxin?fbclid</t>
+          <t>https://www.instagram.com/victorygymofficial_</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6228,7 +6228,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6237,13 +6237,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>87</v>
+        <v>233</v>
       </c>
       <c r="Q62" t="n">
-        <v>116</v>
+        <v>479</v>
       </c>
       <c r="R62" t="n">
-        <v>203</v>
+        <v>712</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6252,17 +6252,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2039687494</t>
+          <t>1000816206</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039687494</t>
+          <t>https://m.place.naver.com/place/1000816206</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6274,29 +6274,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>위PT샵</t>
+          <t>벨루스FIT&amp;PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sdfgg110@naver.com</t>
+          <t>tizn_@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1380-4960</t>
+          <t>0507-1439-2551</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 6 루가빌딩 3층</t>
+          <t>대구광역시 북구 동화천로 245 6층 604호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeba_2017ms.korea</t>
+          <t>https://blog.naver.com/tizn_</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6327,17 +6327,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="R63" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6346,17 +6346,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1564094440</t>
+          <t>2076585284</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564094440</t>
+          <t>https://m.place.naver.com/place/2076585284</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6368,34 +6368,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>빅토리짐 운동센터</t>
+          <t>밸런스핏 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sjsjfit@naver.com</t>
+          <t>balancefit_pt@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>053-325-8334</t>
+          <t>0507-1356-4983</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로106길 18 2F 유산소 및 요가룸 3F 웨이트존</t>
+          <t>대구광역시 북구 침산로 162-8 3층 밸런스핏</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/victorygymofficial_</t>
+          <t>http://pf.kakao.com/_QIETxj/chat</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6416,7 +6416,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>233</v>
+        <v>64</v>
       </c>
       <c r="Q64" t="n">
-        <v>478</v>
+        <v>112</v>
       </c>
       <c r="R64" t="n">
-        <v>711</v>
+        <v>176</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6440,17 +6440,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1000816206</t>
+          <t>1569503169</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1000816206</t>
+          <t>https://m.place.naver.com/place/1569503169</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6462,29 +6462,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>피트파크짐 PT</t>
+          <t>더모스트핏</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>seu0112@naver.com</t>
+          <t>themostfit@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1349-8265</t>
+          <t>0507-1323-4262</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 168 엠브로타워 4층 407호</t>
+          <t>대구광역시 북구 침산로 173 시그니처타워 7층 더모스트핏</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitparkgym?igsh=MzRlODBiNWFlZA==</t>
+          <t>https://www.instagram.com/themostfit_hyun</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6519,13 +6519,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="Q65" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="R65" t="n">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6534,17 +6534,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1036478329</t>
+          <t>1092605247</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036478329</t>
+          <t>https://m.place.naver.com/place/1092605247</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6556,34 +6556,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>스톤짐 복현점</t>
+          <t>사이즈핏</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>stonegym_3@naver.com</t>
+          <t>sizefitpt1989@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1333-5469</t>
+          <t>0507-1380-2027</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+          <t>대구광역시 북구 칠곡중앙대로 291 펫마트 2층 PT전문 사이즈핏</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pQdrxj</t>
+          <t>https://blog.naver.com/sizefitpt1989</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6604,7 +6604,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6613,13 +6613,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>712</v>
+        <v>19</v>
       </c>
       <c r="Q66" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="R66" t="n">
-        <v>886</v>
+        <v>202</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6628,17 +6628,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1113466448</t>
+          <t>1347371484</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113466448</t>
+          <t>https://m.place.naver.com/place/1347371484</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6650,29 +6650,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>바름PT&amp;피트니스</t>
+          <t>국민피티 침산점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>baruemy@naver.com</t>
+          <t>kukminpt@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1326-9724</t>
+          <t>0507-1398-9797</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경중앙로3길 21 라온하제 8층(1층에 CU있어요)</t>
+          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baruemy/224250926219</t>
+          <t>https://www.instagram.com/kukminpt</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6707,13 +6707,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>252</v>
+        <v>700</v>
       </c>
       <c r="Q67" t="n">
-        <v>118</v>
+        <v>1020</v>
       </c>
       <c r="R67" t="n">
-        <v>370</v>
+        <v>1720</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6722,17 +6722,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1848126055</t>
+          <t>1636758988</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1848126055</t>
+          <t>https://m.place.naver.com/place/1636758988</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6744,34 +6744,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>밸런스핏 PT&amp;필라테스</t>
+          <t>로이짐 1:1 PT 침산점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>balancefit_pt@naver.com</t>
+          <t>ejhis12@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1356-4983</t>
+          <t>0507-1426-1060</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 162-8 3층 밸런스핏</t>
+          <t>대구광역시 북구 침산남로 157 4층 로이짐</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_QIETxj/chat</t>
+          <t>https://blog.naver.com/ejhis12</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6792,7 +6792,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6801,13 +6801,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="Q68" t="n">
-        <v>112</v>
+        <v>438</v>
       </c>
       <c r="R68" t="n">
-        <v>176</v>
+        <v>611</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6816,17 +6816,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1569503169</t>
+          <t>1637712306</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569503169</t>
+          <t>https://m.place.naver.com/place/1637712306</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6838,29 +6838,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>벨루스FIT&amp;PT</t>
+          <t>위PT샵</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>tizn_@naver.com</t>
+          <t>sdfgg110@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1439-2551</t>
+          <t>0507-1380-4960</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동화천로 245 6층 604호</t>
+          <t>대구광역시 북구 동천로23길 6 루가빌딩 3층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tizn_</t>
+          <t>https://www.instagram.com/yeba_2017ms.korea</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6891,17 +6891,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="Q69" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="R69" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6910,17 +6910,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2076585284</t>
+          <t>1564094440</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076585284</t>
+          <t>https://m.place.naver.com/place/1564094440</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -6932,29 +6932,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>로이짐 1:1 PT 침산점</t>
+          <t>태고리즘 운동센터</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ejhis12@naver.com</t>
+          <t>gwgtaegorism@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1426-1060</t>
+          <t>0507-1471-1283</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 157 4층 로이짐</t>
+          <t>대구광역시 북구 학정로 551-50 4층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ejhis12</t>
+          <t>https://www.instagram.com/taegorism_rehab/</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6989,13 +6989,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>173</v>
+        <v>47</v>
       </c>
       <c r="Q70" t="n">
-        <v>438</v>
+        <v>108</v>
       </c>
       <c r="R70" t="n">
-        <v>611</v>
+        <v>155</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7004,17 +7004,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1637712306</t>
+          <t>1942933824</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637712306</t>
+          <t>https://m.place.naver.com/place/1942933824</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7026,29 +7026,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>태고리즘 운동센터</t>
+          <t>바름PT&amp;피트니스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>gwgtaegorism@naver.com</t>
+          <t>baruemy@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1471-1283</t>
+          <t>0507-1326-9724</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 551-50 4층</t>
+          <t>대구광역시 북구 연경중앙로3길 21 라온하제 8층(1층에 CU있어요)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taegorism_rehab/</t>
+          <t>https://blog.naver.com/baruemy/224250926219</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7083,13 +7083,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>47</v>
+        <v>252</v>
       </c>
       <c r="Q71" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="R71" t="n">
-        <v>154</v>
+        <v>370</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7098,17 +7098,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1942933824</t>
+          <t>1848126055</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942933824</t>
+          <t>https://m.place.naver.com/place/1848126055</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7120,29 +7120,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>인스타퍼스널트레이닝 PT 침산점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>instarpt2019@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1398-9797</t>
+          <t>0507-1345-9210</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구광역시 북구 침산남로 165 5층 인스타퍼스널트레이닝 PT 침산점</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>https://blog.naver.com/instarpt2019</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7177,13 +7177,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>701</v>
+        <v>190</v>
       </c>
       <c r="Q72" t="n">
-        <v>1008</v>
+        <v>601</v>
       </c>
       <c r="R72" t="n">
-        <v>1709</v>
+        <v>791</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7192,17 +7192,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1174523938</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1174523938</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7214,29 +7214,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>인스타퍼스널트레이닝 PT 침산점</t>
+          <t>피트파크짐 PT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>instarpt2019@naver.com</t>
+          <t>seu0112@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1345-9210</t>
+          <t>0507-1349-8265</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 165 5층 인스타퍼스널트레이닝 PT 침산점</t>
+          <t>대구광역시 북구 침산로 168 엠브로타워 4층 407호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/instarpt2019</t>
+          <t>https://www.instagram.com/fitparkgym?igsh=MzRlODBiNWFlZA==</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7271,13 +7271,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>190</v>
+        <v>47</v>
       </c>
       <c r="Q73" t="n">
-        <v>599</v>
+        <v>149</v>
       </c>
       <c r="R73" t="n">
-        <v>789</v>
+        <v>196</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7286,17 +7286,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1174523938</t>
+          <t>1036478329</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174523938</t>
+          <t>https://m.place.naver.com/place/1036478329</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7308,29 +7308,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>더모스트핏</t>
+          <t>비티비에스 PT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>themostfit@naver.com</t>
+          <t>whgudfo64@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1323-4262</t>
+          <t>0507-1392-3331</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 173 시그니처타워 7층 더모스트핏</t>
+          <t>대구광역시 북구 침산남로 172 6층 비티비에스</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/themostfit_hyun</t>
+          <t>https://blog.naver.com/whgudfo64</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7365,13 +7365,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>12</v>
+        <v>249</v>
       </c>
       <c r="Q74" t="n">
-        <v>24</v>
+        <v>324</v>
       </c>
       <c r="R74" t="n">
-        <v>36</v>
+        <v>573</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7380,17 +7380,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1092605247</t>
+          <t>1999844382</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092605247</t>
+          <t>https://m.place.naver.com/place/1999844382</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7402,29 +7402,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>비티비에스 PT</t>
+          <t>크로스핏마즈</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>whgudfo64@naver.com</t>
+          <t>zx95888@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1392-3331</t>
+          <t>0507-1311-3298</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 172 6층 비티비에스</t>
+          <t>대구광역시 북구 침산로 144 화성투엠A동 지하1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/whgudfo64</t>
+          <t>https://www.instagram.com/marztraining</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7459,13 +7459,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="Q75" t="n">
-        <v>322</v>
+        <v>468</v>
       </c>
       <c r="R75" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7474,17 +7474,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1999844382</t>
+          <t>35720026</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999844382</t>
+          <t>https://m.place.naver.com/place/35720026</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -7496,29 +7496,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>크로스핏마즈</t>
+          <t>플랜PT샵</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>zx95888@naver.com</t>
+          <t>dnwls6050@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1311-3298</t>
+          <t>0507-1439-8242</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 144 화성투엠A동 지하1층</t>
+          <t>대구광역시 북구 학정로 430 3층 304 305호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/marztraining</t>
+          <t>https://blog.naver.com/dnwls6050</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7556,10 +7556,10 @@
         <v>106</v>
       </c>
       <c r="Q76" t="n">
-        <v>468</v>
+        <v>235</v>
       </c>
       <c r="R76" t="n">
-        <v>574</v>
+        <v>341</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7568,17 +7568,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>35720026</t>
+          <t>1053211445</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35720026</t>
+          <t>https://m.place.naver.com/place/1053211445</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/북구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/북구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 북구 동암로 90 3층</t>
+          <t>대구광역시 북구 동암로 90 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구 북구 동북로 279 세림빌딩(신협건물)</t>
+          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mu6u9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+          <t>마인드휘트니스 도남점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>body7677@naver.com</t>
+          <t>mindfitness21@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1388-7681</t>
+          <t>0507-1490-0792</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+          <t>대구광역시 북구 도남중앙로7길 20-4 601호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyengineers_kr</t>
+          <t>https://blog.naver.com/mindfitness21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,19 +789,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c30h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1442</v>
+        <v>824</v>
       </c>
       <c r="Q4" t="n">
-        <v>2054</v>
+        <v>252</v>
       </c>
       <c r="R4" t="n">
-        <v>3496</v>
+        <v>1076</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1961345457</t>
+          <t>1552558325</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961345457</t>
+          <t>https://m.place.naver.com/place/1552558325</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마인드휘트니스 도남점</t>
+          <t>비무브짐24 헬스&amp;PT 천곡점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mindfitness21@naver.com</t>
+          <t>choi_hero1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1490-0792</t>
+          <t>0507-1430-7929</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 북구 도남중앙로7길 20-4 601호</t>
+          <t>울산광역시 북구 달천로 11 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness21</t>
+          <t>https://blog.naver.com/choi_hero1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4srqf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="Q5" t="n">
-        <v>252</v>
+        <v>558</v>
       </c>
       <c r="R5" t="n">
-        <v>1076</v>
+        <v>1379</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1552558325</t>
+          <t>1018353491</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1552558325</t>
+          <t>https://m.place.naver.com/place/1018353491</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이지피트니스</t>
+          <t>S GYM 덕천점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>easyfitness01@naver.com</t>
+          <t>sgym_deokcheon@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-1029</t>
+          <t>0507-1353-4111</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
+          <t>부산광역시 북구 의성로 91 3층 S GYM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/easyfitness01</t>
+          <t>https://www.instagram.com/sgym_deokcheon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,19 +977,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dzy1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>604</v>
+        <v>349</v>
       </c>
       <c r="Q6" t="n">
-        <v>286</v>
+        <v>647</v>
       </c>
       <c r="R6" t="n">
-        <v>890</v>
+        <v>996</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1129757069</t>
+          <t>1416099896</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129757069</t>
+          <t>https://m.place.naver.com/place/1416099896</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디채널 침산점</t>
+          <t>이지피트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodycs@naver.com</t>
+          <t>easyfitness01@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1342-4850</t>
+          <t>0507-1350-1029</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 북구 침산남로 154 10층</t>
+          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_chimsan</t>
+          <t>https://blog.naver.com/easyfitness01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49li4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>177</v>
+        <v>604</v>
       </c>
       <c r="Q7" t="n">
-        <v>1529</v>
+        <v>286</v>
       </c>
       <c r="R7" t="n">
-        <v>1706</v>
+        <v>890</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1023076989</t>
+          <t>1129757069</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023076989</t>
+          <t>https://m.place.naver.com/place/1129757069</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>크로스핏타임 칠곡점</t>
+          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>timegym2021@naver.com</t>
+          <t>body7677@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1355-3967</t>
+          <t>0507-1388-7681</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 북구 팔거천동로 224 지하1층</t>
+          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/shs4uWwf</t>
+          <t>https://www.instagram.com/bodyengineers_kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,17 +1170,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zlio</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>69</v>
+        <v>1442</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>2054</v>
       </c>
       <c r="R8" t="n">
-        <v>106</v>
+        <v>3496</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1151810571</t>
+          <t>1961345457</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1151810571</t>
+          <t>https://m.place.naver.com/place/1961345457</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,34 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>바디채널 침산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>bodycs@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1398-9797</t>
+          <t>0507-1342-4850</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구광역시 북구 침산남로 154 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>https://www.instagram.com/bodychannel_chimsan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1288,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f9se</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>700</v>
+        <v>177</v>
       </c>
       <c r="Q9" t="n">
-        <v>1023</v>
+        <v>1529</v>
       </c>
       <c r="R9" t="n">
-        <v>1723</v>
+        <v>1706</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1023076989</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1023076989</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스톤짐 복현점</t>
+          <t>국민피티 침산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>stonegym_3@naver.com</t>
+          <t>kukminpt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1333-5469</t>
+          <t>0507-1398-9797</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 북구 동북로 244 BL타워 13층</t>
+          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pQdrxj</t>
+          <t>https://www.instagram.com/kukminpt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1386,17 +1358,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wtum</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="Q10" t="n">
-        <v>176</v>
+        <v>1021</v>
       </c>
       <c r="R10" t="n">
-        <v>890</v>
+        <v>1721</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1113466448</t>
+          <t>1636758988</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113466448</t>
+          <t>https://m.place.naver.com/place/1636758988</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,91 +1410,181 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엑스알핏</t>
+          <t>스톤짐 복현점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>xrfit@naver.com</t>
+          <t>stonegym_3@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1379-4047</t>
+          <t>0507-1333-5469</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 북구 중앙대로 528 8층</t>
+          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>http://pf.kakao.com/_pQdrxj</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>715</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>179</v>
+      </c>
+      <c r="R11" t="n">
+        <v>894</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1113466448</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1113466448</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>엑스알핏</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>xrfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1379-4047</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 중앙대로 528 8층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>https://blog.naver.com/xrfit</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4okn6y</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>8</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>30</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>38</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>2081794552</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2081794552</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/북구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/북구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동암로 90 3층</t>
+          <t>대구 북구 동암로 90 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
+          <t>대구 북구 동북로 279 세림빌딩(신협건물)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mave000</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +690,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mu6u9</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Q3" t="n">
         <v>984</v>
       </c>
       <c r="R3" t="n">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -769,12 +773,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 도남중앙로7길 20-4 601호</t>
+          <t>대구 북구 도남중앙로7길 20-4 601호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mindfitness21</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4srqf</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,10 +817,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="Q4" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R4" t="n">
         <v>1076</v>
@@ -834,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 천곡점</t>
+          <t>S GYM 덕천점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>choi_hero1@naver.com</t>
+          <t>sgym_deokcheon@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1430-7929</t>
+          <t>0507-1353-4111</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>울산광역시 북구 달천로 11 5층</t>
+          <t>부산 북구 의성로 91 3층 S GYM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/choi_hero1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +886,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4slc8</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>821</v>
+        <v>349</v>
       </c>
       <c r="Q5" t="n">
-        <v>558</v>
+        <v>647</v>
       </c>
       <c r="R5" t="n">
-        <v>1379</v>
+        <v>996</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1018353491</t>
+          <t>1416099896</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018353491</t>
+          <t>https://m.place.naver.com/place/1416099896</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S GYM 덕천점</t>
+          <t>이지피트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sgym_deokcheon@naver.com</t>
+          <t>easyfitness01@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1353-4111</t>
+          <t>0507-1350-1029</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 북구 의성로 91 3층 S GYM</t>
+          <t>대구 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sgym_deokcheon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dzy1</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>349</v>
+        <v>604</v>
       </c>
       <c r="Q6" t="n">
-        <v>647</v>
+        <v>287</v>
       </c>
       <c r="R6" t="n">
-        <v>996</v>
+        <v>891</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1416099896</t>
+          <t>1129757069</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1416099896</t>
+          <t>https://m.place.naver.com/place/1129757069</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>이지피트니스</t>
+          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>easyfitness01@naver.com</t>
+          <t>body7677@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1350-1029</t>
+          <t>0507-1388-7681</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
+          <t>대구 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/easyfitness01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,20 +1082,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4c30h</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>604</v>
+        <v>1442</v>
       </c>
       <c r="Q7" t="n">
-        <v>286</v>
+        <v>2055</v>
       </c>
       <c r="R7" t="n">
-        <v>890</v>
+        <v>3497</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1129757069</t>
+          <t>1961345457</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129757069</t>
+          <t>https://m.place.naver.com/place/1961345457</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+          <t>바디채널 침산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>body7677@naver.com</t>
+          <t>bodycs@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1388-7681</t>
+          <t>0507-1342-4850</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+          <t>대구 북구 침산남로 154 10층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyengineers_kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1170,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49li4</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1442</v>
+        <v>177</v>
       </c>
       <c r="Q8" t="n">
-        <v>2054</v>
+        <v>1529</v>
       </c>
       <c r="R8" t="n">
-        <v>3496</v>
+        <v>1706</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1961345457</t>
+          <t>1023076989</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961345457</t>
+          <t>https://m.place.naver.com/place/1023076989</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디채널 침산점</t>
+          <t>스톤짐 복현점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodycs@naver.com</t>
+          <t>stonegym_3@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1342-4850</t>
+          <t>0507-1333-5469</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 154 10층</t>
+          <t>대구 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodychannel_chimsan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1264,13 +1288,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wtum</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>177</v>
+        <v>715</v>
       </c>
       <c r="Q9" t="n">
-        <v>1529</v>
+        <v>180</v>
       </c>
       <c r="R9" t="n">
-        <v>1706</v>
+        <v>895</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1023076989</t>
+          <t>1113466448</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023076989</t>
+          <t>https://m.place.naver.com/place/1113466448</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1361,12 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,7 +1376,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1358,10 +1386,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9se</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1376,10 +1408,10 @@
         <v>700</v>
       </c>
       <c r="Q10" t="n">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="R10" t="n">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1398,7 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1442,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스톤짐 복현점</t>
+          <t>엑스알핏</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>stonegym_3@naver.com</t>
+          <t>xrfit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1333-5469</t>
+          <t>0507-1379-4047</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 BL타워 13층</t>
+          <t>대구 북구 중앙대로 528 8층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pQdrxj</t>
+          <t>https://blog.naver.com/xrfit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,18 +1479,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4okn6y</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>715</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="R11" t="n">
-        <v>894</v>
+        <v>38</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,111 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1113466448</t>
+          <t>2081794552</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113466448</t>
+          <t>https://m.place.naver.com/place/2081794552</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>엑스알핏</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>xrfit@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1379-4047</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대구광역시 북구 중앙대로 528 8층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/xrfit</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>30</v>
-      </c>
-      <c r="R12" t="n">
-        <v>38</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2081794552</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2081794552</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/북구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/북구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mave000</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="Q3" t="n">
         <v>984</v>
       </c>
       <c r="R3" t="n">
-        <v>3007</v>
+        <v>3010</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mindfitness21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="Q4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R4" t="n">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 북구 의성로 91 3층 S GYM</t>
+          <t>부산광역시 북구 의성로 91 3층 S GYM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sgym_deokcheon</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -896,14 +896,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4slc8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -952,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>이지피트니스</t>
+          <t>버거짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>easyfitness01@naver.com</t>
+          <t>burgergym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1350-1029</t>
+          <t>0507-1400-9556</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
+          <t>대구 북구 팔달로 209 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/burger_gym_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,7 +980,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -999,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dzy1</t>
+          <t>https://talk.naver.com/ct/w5xcwn</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>604</v>
+        <v>155</v>
       </c>
       <c r="Q6" t="n">
-        <v>287</v>
+        <v>365</v>
       </c>
       <c r="R6" t="n">
-        <v>891</v>
+        <v>520</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1129757069</t>
+          <t>1590239180</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129757069</t>
+          <t>https://m.place.naver.com/place/1590239180</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+          <t>이지피트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>body7677@naver.com</t>
+          <t>easyfitness01@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1388-7681</t>
+          <t>0507-1350-1029</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+          <t>대구 북구 칠곡중앙대로 373 2층 엘리베이터 앞</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/easyfitness01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1078,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c30h</t>
+          <t>https://talk.naver.com/ct/w4dzy1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1442</v>
+        <v>604</v>
       </c>
       <c r="Q7" t="n">
-        <v>2055</v>
+        <v>287</v>
       </c>
       <c r="R7" t="n">
-        <v>3497</v>
+        <v>891</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1961345457</t>
+          <t>1129757069</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961345457</t>
+          <t>https://m.place.naver.com/place/1129757069</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디채널 침산점</t>
+          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodycs@naver.com</t>
+          <t>body7677@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1342-4850</t>
+          <t>0507-1388-7681</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 북구 침산남로 154 10층</t>
+          <t>대구 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bodyengineers_kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1176,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1195,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49li4</t>
+          <t>https://talk.naver.com/ct/w4c30h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>177</v>
+        <v>1443</v>
       </c>
       <c r="Q8" t="n">
-        <v>1529</v>
+        <v>2055</v>
       </c>
       <c r="R8" t="n">
-        <v>1706</v>
+        <v>3498</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1023076989</t>
+          <t>1961345457</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023076989</t>
+          <t>https://m.place.naver.com/place/1961345457</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스톤짐 복현점</t>
+          <t>바디채널 침산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>stonegym_3@naver.com</t>
+          <t>bodycs@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1333-5469</t>
+          <t>0507-1342-4850</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 북구 동북로 244 BL타워 13층</t>
+          <t>대구 북구 침산남로 154 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bodychannel_chimsan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,7 +1274,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1293,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wtum</t>
+          <t>https://talk.naver.com/ct/w49li4</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>715</v>
+        <v>177</v>
       </c>
       <c r="Q9" t="n">
-        <v>180</v>
+        <v>1529</v>
       </c>
       <c r="R9" t="n">
-        <v>895</v>
+        <v>1706</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1113466448</t>
+          <t>1023076989</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113466448</t>
+          <t>https://m.place.naver.com/place/1023076989</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1344,39 +1340,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>스톤짐 복현점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>stonegym_3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1398-9797</t>
+          <t>0507-1333-5469</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구 북구 동북로 244 BL타워 13층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_pQdrxj</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,12 +1387,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f9se</t>
+          <t>https://talk.naver.com/ct/w5wtum</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="Q10" t="n">
-        <v>1022</v>
+        <v>180</v>
       </c>
       <c r="R10" t="n">
-        <v>1722</v>
+        <v>895</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1113466448</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1113466448</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1442,93 +1438,191 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엑스알핏</t>
+          <t>국민피티 침산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>xrfit@naver.com</t>
+          <t>kukminpt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1379-4047</t>
+          <t>0507-1398-9797</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kukminpt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9se</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>700</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1022</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1722</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1636758988</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1636758988</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>엑스알핏</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>xrfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1379-4047</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>대구 북구 중앙대로 528 8층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/xrfit</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4okn6y</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>8</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>30</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>38</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>2081794552</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2081794552</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
